--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6815-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6815-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89E07C9F-60D3-4E9E-974A-F2A5FD550509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06111523-3F7D-4BBE-A859-8804F8BBA9F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{2208EC66-0024-4419-9966-689BCA2C2A39}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C1E006E4-EA42-4367-A2A3-5177810180D2}"/>
   </bookViews>
   <sheets>
     <sheet name="6815-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1439,25 +1439,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB23EF6-36C5-489A-B9BD-3CAF7C753F57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F787A5-37BA-4A61-B7D4-3EB584993CF7}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1485,7 +1485,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1611,7 +1611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2023</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2022</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2021</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>32</v>
       </c>
